--- a/data/emergency.xlsx
+++ b/data/emergency.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C427F71-2C58-415D-BCD3-CF7D694AA9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2759141-0F33-4B3B-8A9A-4ADC63F94EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E1E97517-FB75-4300-A546-6D61B4406E42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>

--- a/data/emergency.xlsx
+++ b/data/emergency.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E933887-89D8-4B54-B238-63E37ACCF53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61F2F28-0E8F-49D9-95F7-309B9519B3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E1E97517-FB75-4300-A546-6D61B4406E42}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="97">
   <si>
     <t>Latitude</t>
   </si>
@@ -126,135 +126,9 @@
     <t>E012</t>
   </si>
   <si>
-    <t>Jl, Laksda Adisucipto No,96, Gowok, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,3/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/1tc5gVCekgqJ84GM7</t>
-  </si>
-  <si>
-    <t>images\E001,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Seturan Baru, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,5/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/8XVVMRrw4CWkr26k9</t>
-  </si>
-  <si>
-    <t>Jl, Ipda Tut Harsono Jl, Melati Wetan No,53, Muja Muju, Kec, Umbulharjo, Kota Yogyakarta, Daerah Istimewa Yogyakarta 55165</t>
-  </si>
-  <si>
-    <t>4,8/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/wwaF4Ahgr5sdn5XJ7</t>
-  </si>
-  <si>
     <t>Sagan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
   </si>
   <si>
-    <t>https://maps,app,goo,gl/ZzhXtQWWRTf4Vnk27</t>
-  </si>
-  <si>
-    <t>08,00 - 15,00</t>
-  </si>
-  <si>
-    <t>Jl, Pintu Selatan UPN Gorongan, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>4,0/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/XuDwUsmqezaZJW5U7</t>
-  </si>
-  <si>
-    <t>images\E005,jpg</t>
-  </si>
-  <si>
-    <t>06,00–22,00</t>
-  </si>
-  <si>
-    <t>Jl, Babarsari, Caturtunggal, Depok, Sleman</t>
-  </si>
-  <si>
-    <t>4,1/5,0</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/mbYPmPoBmo8azzhG6</t>
-  </si>
-  <si>
-    <t>images\E006,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Lembah UGM, Karang Malang, Caturtunggal, Depok, Sleman 55284</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/Y2NDpmasJhUnM3eX8</t>
-  </si>
-  <si>
-    <t>images\E007,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Kabupaten, Trihanggo, Kec, Gamping, Kabupaten Sleman 55291</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/TxLLgBRR573KTQsG8</t>
-  </si>
-  <si>
-    <t>images\E008,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Ring Road Utara, Sanggrahan, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/8iVHeVNPw9wwyzhC6</t>
-  </si>
-  <si>
-    <t>images\E009,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Ipda Tut Harsono, Muja Muju, Kec, Umbulharjo, Kota Yogyakarta, DIY 55165</t>
-  </si>
-  <si>
-    <t>4,7/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/s3KytaSrx841UmJT9</t>
-  </si>
-  <si>
-    <t>images\E010,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Laksda Adisucipto No,32, Ambarukmo, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>4,2/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/ATxnptNWmH4n2mycA</t>
-  </si>
-  <si>
-    <t>images\E011,jpg</t>
-  </si>
-  <si>
-    <t>07,30 - 16,00</t>
-  </si>
-  <si>
-    <t>Jl, Kaliurang No,KM,7, RW,8, Ngabean Kulon, Sinduharjo, Sleman, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
-  </si>
-  <si>
-    <t>2,0/5</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/wgbcPHdrAV6LYEAY7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hari_operasional </t>
   </si>
   <si>
@@ -279,115 +153,169 @@
     <t xml:space="preserve">Senin - Minggu </t>
   </si>
   <si>
-    <t>-7,783425284431668</t>
-  </si>
-  <si>
-    <t>110,40294661388249</t>
-  </si>
-  <si>
     <t>Ya</t>
   </si>
   <si>
     <t>089699492959</t>
   </si>
   <si>
-    <t>-7,7661566396731105</t>
-  </si>
-  <si>
-    <t>110,40850091024772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\E002,jpg </t>
-  </si>
-  <si>
     <t xml:space="preserve">Instalasi Gawat Darurat (IGD) Rumah Sakit Happy Land </t>
   </si>
   <si>
-    <t>-7,794156876922177</t>
-  </si>
-  <si>
-    <t>110,39264508122194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\E003,jpg </t>
-  </si>
-  <si>
     <t xml:space="preserve">Damkar UGM </t>
   </si>
   <si>
-    <t>-7,775337635523675</t>
-  </si>
-  <si>
-    <t>110,37960783095677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\E004,jpg </t>
-  </si>
-  <si>
     <t xml:space="preserve">Klinik Pratama UPN "Veteran" Yogyakarta </t>
   </si>
   <si>
-    <t>-7,7628556685118495</t>
-  </si>
-  <si>
-    <t>110,40772511348271</t>
-  </si>
-  <si>
     <t>Tidak</t>
   </si>
   <si>
-    <t>-7,773703006145326</t>
-  </si>
-  <si>
-    <t>110,41035675396712</t>
-  </si>
-  <si>
-    <t>-7,761969351079371</t>
-  </si>
-  <si>
-    <t>110,41532245212167</t>
-  </si>
-  <si>
-    <t>-7,743381572236378</t>
-  </si>
-  <si>
-    <t>110,3502590134826</t>
-  </si>
-  <si>
     <t xml:space="preserve">Polda DIY </t>
   </si>
   <si>
-    <t>-7,757727726668868</t>
-  </si>
-  <si>
-    <t>110,40058596294900</t>
-  </si>
-  <si>
-    <t>-7,798677942377662</t>
-  </si>
-  <si>
-    <t>110,39236596309500</t>
-  </si>
-  <si>
-    <t>-7,7832460822691200</t>
-  </si>
-  <si>
-    <t>110,40669607386313</t>
-  </si>
-  <si>
     <t xml:space="preserve">PLN Gardu Induk Keuntungan </t>
   </si>
   <si>
     <t>(0274)12345</t>
   </si>
   <si>
-    <t>-7,735693422077360</t>
-  </si>
-  <si>
-    <t>110,39289790153300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\E012,jpg </t>
+    <t>08.00 - 15.00</t>
+  </si>
+  <si>
+    <t>06.00–22.00</t>
+  </si>
+  <si>
+    <t>07.30 - 16.00</t>
+  </si>
+  <si>
+    <t>Jl. Laksda Adisucipto No,96, Gowok, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Seturan Baru, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Ipda Tut Harsono Jl. Melati Wetan No,53, Muja Muju, Kec, Umbulharjo, Kota Yogyakarta, Daerah Istimewa Yogyakarta 55165</t>
+  </si>
+  <si>
+    <t>Jl. Pintu Selatan UPN Gorongan, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Jl. Babarsari, Caturtunggal, Depok, Sleman</t>
+  </si>
+  <si>
+    <t>Jl. Lembah UGM, Karang Malang, Caturtunggal, Depok, Sleman 55284</t>
+  </si>
+  <si>
+    <t>Jl. Kabupaten, Trihanggo, Kec, Gamping, Kabupaten Sleman 55291</t>
+  </si>
+  <si>
+    <t>Jl. Ring Road Utara, Sanggrahan, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
+  </si>
+  <si>
+    <t>Jl. Ipda Tut Harsono, Muja Muju, Kec, Umbulharjo, Kota Yogyakarta, DIY 55165</t>
+  </si>
+  <si>
+    <t>Jl. Laksda Adisucipto No,32, Ambarukmo, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Kaliurang No,KM,7, RW,8, Ngabean Kulon, Sinduharjo, Sleman, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>4.3/5.0</t>
+  </si>
+  <si>
+    <t>4.5/5.0</t>
+  </si>
+  <si>
+    <t>4.8/5.0</t>
+  </si>
+  <si>
+    <t>4.0/5.0</t>
+  </si>
+  <si>
+    <t>4.1/5.0</t>
+  </si>
+  <si>
+    <t>4.7/5</t>
+  </si>
+  <si>
+    <t>4.2/5</t>
+  </si>
+  <si>
+    <t>2.0/5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1tc5gVCekgqJ84GM7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8XVVMRrw4CWkr26k9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wwaF4Ahgr5sdn5XJ7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ZzhXtQWWRTf4Vnk27</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/XuDwUsmqezaZJW5U7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mbYPmPoBmo8azzhG6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Y2NDpmasJhUnM3eX8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/TxLLgBRR573KTQsG8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8iVHeVNPw9wwyzhC6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/s3KytaSrx841UmJT9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ATxnptNWmH4n2mycA</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wgbcPHdrAV6LYEAY7</t>
+  </si>
+  <si>
+    <t>images\E001.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\E002.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\E003.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\E004.jpg </t>
+  </si>
+  <si>
+    <t>images\E005.jpg</t>
+  </si>
+  <si>
+    <t>images\E006.jpg</t>
+  </si>
+  <si>
+    <t>images\E007.jpg</t>
+  </si>
+  <si>
+    <t>images\E008.jpg</t>
+  </si>
+  <si>
+    <t>images\E009.jpg</t>
+  </si>
+  <si>
+    <t>images\E010.jpg</t>
+  </si>
+  <si>
+    <t>images\E011.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\E012.jpg </t>
   </si>
 </sst>
 </file>
@@ -876,16 +804,16 @@
         <v>14</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>0</v>
@@ -894,7 +822,7 @@
         <v>1</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>3</v>
@@ -906,7 +834,7 @@
         <v>2</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -914,41 +842,41 @@
         <v>15</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="G2" s="10"/>
-      <c r="H2" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="11" t="s">
+      <c r="H2" s="11">
+        <v>-7.7834252844316598</v>
+      </c>
+      <c r="I2" s="11">
+        <v>110.40294661388199</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>36</v>
-      </c>
       <c r="M2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -956,43 +884,43 @@
         <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>89</v>
+        <v>43</v>
+      </c>
+      <c r="H3" s="11">
+        <v>-7.7661566396731097</v>
+      </c>
+      <c r="I3" s="11">
+        <v>110.408500910247</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1000,43 +928,43 @@
         <v>17</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>93</v>
+      <c r="H4" s="11">
+        <v>-7.7941568769221696</v>
+      </c>
+      <c r="I4" s="11">
+        <v>110.392645081221</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="K4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1044,41 +972,41 @@
         <v>19</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G5" s="10"/>
-      <c r="H5" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>97</v>
+      <c r="H5" s="11">
+        <v>-7.7753376355236696</v>
+      </c>
+      <c r="I5" s="11">
+        <v>110.379607830956</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1086,41 +1014,41 @@
         <v>20</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G6" s="10"/>
-      <c r="H6" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>101</v>
+      <c r="H6" s="11">
+        <v>-7.7628556685118397</v>
+      </c>
+      <c r="I6" s="11">
+        <v>110.407725113482</v>
       </c>
       <c r="J6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1134,37 +1062,37 @@
         <v>5</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>104</v>
+      <c r="H7" s="11">
+        <v>-7.7737030061453201</v>
+      </c>
+      <c r="I7" s="11">
+        <v>110.41035675396699</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1178,37 +1106,37 @@
         <v>5</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>106</v>
+      <c r="H8" s="11">
+        <v>-7.7619693510793697</v>
+      </c>
+      <c r="I8" s="11">
+        <v>110.415322452121</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="M8" s="8" t="s">
         <v>7</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1222,37 +1150,37 @@
         <v>5</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>108</v>
+      <c r="H9" s="11">
+        <v>-7.7433815722363697</v>
+      </c>
+      <c r="I9" s="11">
+        <v>110.350259013482</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>7</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1260,13 +1188,13 @@
         <v>27</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>6</v>
@@ -1277,26 +1205,26 @@
       <c r="G10" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>111</v>
+      <c r="H10" s="11">
+        <v>-7.7577277266688602</v>
+      </c>
+      <c r="I10" s="18">
+        <v>110.40058596294899</v>
       </c>
       <c r="J10" s="15" t="s">
         <v>7</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="M10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1310,37 +1238,37 @@
         <v>5</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>113</v>
+      <c r="H11" s="11">
+        <v>-7.79867794237766</v>
+      </c>
+      <c r="I11" s="18">
+        <v>110.392365963095</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>7</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1354,37 +1282,37 @@
         <v>5</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>115</v>
+      <c r="H12" s="18">
+        <v>-7.7832460822691196</v>
+      </c>
+      <c r="I12" s="18">
+        <v>110.406696073863</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="M12" s="8" t="s">
         <v>7</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
@@ -1392,59 +1320,59 @@
         <v>32</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="18">
+        <v>-7.7356934220773601</v>
+      </c>
+      <c r="I13" s="18">
+        <v>110.392897901533</v>
+      </c>
+      <c r="J13" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>74</v>
-      </c>
       <c r="K13" s="12" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="M13" s="15" t="s">
         <v>7</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" xr:uid="{9CCC22E3-1838-48E1-AEEE-181A806EEEF1}"/>
-    <hyperlink ref="K3" r:id="rId2" xr:uid="{E70CE396-7817-42E0-B7DC-8C40A7AA5D9E}"/>
-    <hyperlink ref="K4" r:id="rId3" xr:uid="{453BBD94-5DDB-45B5-B2AF-7FDB75E9B79B}"/>
-    <hyperlink ref="K5" r:id="rId4" xr:uid="{99AAE41C-CFCE-424A-B93F-C2308E68E95A}"/>
-    <hyperlink ref="K6" r:id="rId5" xr:uid="{80791F83-3ECE-4863-8DCE-F3F124EBA70C}"/>
-    <hyperlink ref="K7" r:id="rId6" xr:uid="{086170E1-3990-4AA3-AC73-CFCD5717935D}"/>
-    <hyperlink ref="K8" r:id="rId7" xr:uid="{6CDC97F7-E00C-4822-B5D4-0A90070490E1}"/>
-    <hyperlink ref="K9" r:id="rId8" xr:uid="{611274C1-7F8D-49E4-812F-0B6F980455B9}"/>
-    <hyperlink ref="K10" r:id="rId9" xr:uid="{F0FDFAE9-5D25-4474-9365-4703ADC25668}"/>
-    <hyperlink ref="K11" r:id="rId10" xr:uid="{A81A9B6C-35BD-48BB-9EBC-EB0AD6AAF9AD}"/>
-    <hyperlink ref="K12" r:id="rId11" xr:uid="{F3B43F08-8975-43AE-848F-9AC8BE3B347C}"/>
-    <hyperlink ref="K13" r:id="rId12" xr:uid="{B69B2A6C-A0E7-46A4-92D2-DD1ECE08CBC0}"/>
+    <hyperlink ref="K2" r:id="rId1" display="https://maps,app,goo,gl/1tc5gVCekgqJ84GM7" xr:uid="{9CCC22E3-1838-48E1-AEEE-181A806EEEF1}"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://maps,app,goo,gl/8XVVMRrw4CWkr26k9" xr:uid="{E70CE396-7817-42E0-B7DC-8C40A7AA5D9E}"/>
+    <hyperlink ref="K4" r:id="rId3" display="https://maps,app,goo,gl/wwaF4Ahgr5sdn5XJ7" xr:uid="{453BBD94-5DDB-45B5-B2AF-7FDB75E9B79B}"/>
+    <hyperlink ref="K5" r:id="rId4" display="https://maps,app,goo,gl/ZzhXtQWWRTf4Vnk27" xr:uid="{99AAE41C-CFCE-424A-B93F-C2308E68E95A}"/>
+    <hyperlink ref="K6" r:id="rId5" display="https://maps,app,goo,gl/XuDwUsmqezaZJW5U7" xr:uid="{80791F83-3ECE-4863-8DCE-F3F124EBA70C}"/>
+    <hyperlink ref="K7" r:id="rId6" display="https://maps,app,goo,gl/mbYPmPoBmo8azzhG6" xr:uid="{086170E1-3990-4AA3-AC73-CFCD5717935D}"/>
+    <hyperlink ref="K8" r:id="rId7" display="https://maps,app,goo,gl/Y2NDpmasJhUnM3eX8" xr:uid="{6CDC97F7-E00C-4822-B5D4-0A90070490E1}"/>
+    <hyperlink ref="K9" r:id="rId8" display="https://maps,app,goo,gl/TxLLgBRR573KTQsG8" xr:uid="{611274C1-7F8D-49E4-812F-0B6F980455B9}"/>
+    <hyperlink ref="K10" r:id="rId9" display="https://maps,app,goo,gl/8iVHeVNPw9wwyzhC6" xr:uid="{F0FDFAE9-5D25-4474-9365-4703ADC25668}"/>
+    <hyperlink ref="K11" r:id="rId10" display="https://maps,app,goo,gl/s3KytaSrx841UmJT9" xr:uid="{A81A9B6C-35BD-48BB-9EBC-EB0AD6AAF9AD}"/>
+    <hyperlink ref="K12" r:id="rId11" display="https://maps,app,goo,gl/ATxnptNWmH4n2mycA" xr:uid="{F3B43F08-8975-43AE-848F-9AC8BE3B347C}"/>
+    <hyperlink ref="K13" r:id="rId12" display="https://maps,app,goo,gl/wgbcPHdrAV6LYEAY7" xr:uid="{B69B2A6C-A0E7-46A4-92D2-DD1ECE08CBC0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/emergency.xlsx
+++ b/data/emergency.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61F2F28-0E8F-49D9-95F7-309B9519B3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772BC90D-4BA1-4516-96D4-94A53490C961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E1E97517-FB75-4300-A546-6D61B4406E42}"/>
   </bookViews>
@@ -395,16 +395,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -413,15 +413,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -437,7 +434,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -446,19 +443,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -803,559 +796,559 @@
       <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11">
+      <c r="G2" s="9"/>
+      <c r="H2" s="10">
         <v>-7.7834252844316598</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>110.40294661388199</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="M2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" s="13" t="s">
+      <c r="M2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="10">
         <v>-7.7661566396731097</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="10">
         <v>110.408500910247</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" s="13" t="s">
+      <c r="M3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <v>-7.7941568769221696</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="10">
         <v>110.392645081221</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="M4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N4" s="13" t="s">
+      <c r="M4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="11">
+      <c r="G5" s="9"/>
+      <c r="H5" s="10">
         <v>-7.7753376355236696</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="10">
         <v>110.379607830956</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="12" t="s">
+      <c r="J5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="M5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N5" s="13" t="s">
+      <c r="M5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N5" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="11">
+      <c r="G6" s="9"/>
+      <c r="H6" s="10">
         <v>-7.7628556685118397</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="10">
         <v>110.407725113482</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="M6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N6" s="13" t="s">
+      <c r="M6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="11">
+      <c r="G7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="10">
         <v>-7.7737030061453201</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="10">
         <v>110.41035675396699</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="M7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N7" s="13" t="s">
+      <c r="M7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <v>-7.7619693510793697</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="10">
         <v>110.415322452121</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N8" s="13" t="s">
+      <c r="M8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N8" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="11">
+      <c r="G9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="10">
         <v>-7.7433815722363697</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="10">
         <v>110.350259013482</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="M9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N9" s="13" t="s">
+      <c r="M9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <v>-7.7577277266688602</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="16">
         <v>110.40058596294899</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="K10" s="12" t="s">
+      <c r="J10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="M10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N10" s="13" t="s">
+      <c r="M10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N10" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <v>-7.79867794237766</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="16">
         <v>110.392365963095</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="M11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N11" s="13" t="s">
+      <c r="M11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N11" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="16">
         <v>-7.7832460822691196</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="16">
         <v>110.406696073863</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="M12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N12" s="13" t="s">
+      <c r="M12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N12" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="16">
         <v>-7.7356934220773601</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="16">
         <v>110.392897901533</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="M13" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="N13" s="13" t="s">
+      <c r="M13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N13" s="12" t="s">
         <v>47</v>
       </c>
     </row>
